--- a/deliverables/入力分類表_確定.xlsx
+++ b/deliverables/入力分類表_確定.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>空にする</t>
+          <t>「株式会社〇〇」(仮の社名)に置き換える(整形版・テンプレート版とも)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>社名</t>
+          <t>社名(ご指示で仮名に変更)</t>
         </is>
       </c>
     </row>
